--- a/artfynd/A 32206-2024 artfynd.xlsx
+++ b/artfynd/A 32206-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820715</v>
+        <v>119820709</v>
       </c>
       <c r="B2" t="n">
-        <v>77910</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413072</v>
+        <v>413204</v>
       </c>
       <c r="R2" t="n">
-        <v>6812749</v>
+        <v>6812702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820709</v>
+        <v>119820715</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>77910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413204</v>
+        <v>413072</v>
       </c>
       <c r="R3" t="n">
-        <v>6812702</v>
+        <v>6812749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32206-2024 artfynd.xlsx
+++ b/artfynd/A 32206-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820709</v>
+        <v>119820715</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>77910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413204</v>
+        <v>413072</v>
       </c>
       <c r="R2" t="n">
-        <v>6812702</v>
+        <v>6812749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820715</v>
+        <v>119820709</v>
       </c>
       <c r="B3" t="n">
-        <v>77910</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413072</v>
+        <v>413204</v>
       </c>
       <c r="R3" t="n">
-        <v>6812749</v>
+        <v>6812702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32206-2024 artfynd.xlsx
+++ b/artfynd/A 32206-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119820709</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>119820715</v>
       </c>
       <c r="B3" t="n">
-        <v>77910</v>
+        <v>77926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32206-2024 artfynd.xlsx
+++ b/artfynd/A 32206-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820712</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>